--- a/docs/タスク設計書_v2.xlsx
+++ b/docs/タスク設計書_v2.xlsx
@@ -11,6 +11,7 @@
     <sheet name="タスク一覧・完了条件" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="タスク別入力項目" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="作業手順テンプレート" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="画面構成" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -206,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -326,6 +327,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,12 +850,12 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>依存関係の手動編集</t>
+          <t>依存関係の編集</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>【管理担当のみ】タスク詳細のサイドバー下部「依存関係を編集」から手動で前後関係を変更できる。通常案件では使用しない。特殊なフロー変更が必要な場合に管理担当が使用する。</t>
+          <t>依存関係はテンプレートのフロールールに基づき自動生成のみ。手動編集UIは提供しない（運用簡素化のため）。</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -2732,7 +2745,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>※ 各タスクのカテゴリに応じて、タスク詳細画面に専用の入力フォームが表示されます。データはext_data（JSONB）に保存されます。</t>
+          <t>※ 各タスクのカテゴリに応じて、タスク詳細画面の最下部「📝 作業内容」セクションに専用の入力フォームが表示されます（カテゴリ別にセクション名は変えず「作業内容」で統一）。データはext_data（JSONB）に保存されます。</t>
         </is>
       </c>
     </row>
@@ -4611,4 +4624,437 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>画面構成・運用ルール（現場向けUI最適化）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>※ 「複数のパートタイマーが日替わりで着手前タスクをピックアップ → 完了 or 途中で帰る」という運用を前提に最適化された画面構成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>■ タスク詳細画面の構成（上から順）</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>目的・内容</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ヘッダー</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>ID / フェーズ / カテゴリ バッジ、タスク名、案件リンク、着手/完了ボタン、ステータスフロー（着手前→対応中→完了）</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>着手ボタン下に「作業を始める前に押す」、完了ボタン下に「完了条件を満たしたら押す」のヒント表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>👉 今やること</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>✅ 完了条件（このタスクを完了にするタイミング）／📋 作業手順（チェックリスト形式）を最上段に強調表示</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>完了条件は src/lib/taskCompletionConditions.ts、作業手順は task_templates.procedure_text から取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>📝 基本情報</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>件名・起票日・期限・ステータス・優先度・フェーズ・カテゴリ・備考</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>旧「内容・分類」セクションを統合。表題（作業内容）フィールドは作業手順と重複するため削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>👤 着手者・作業履歴</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>現在の着手者を緑色カードで表示。下部にこのタスクの活動履歴</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>未着手の場合は「まだ誰も着手していません」＋ ▶着手するボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>📝 作業内容</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>カテゴリ別の入力フォーム（請求先市町村・到着日など）</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>全カテゴリでセクション名を「作業内容」に統一。カテゴリ識別はヘッダーのバッジで行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>■ タスク一覧画面の運用ルール</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>仕様</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>デフォルトフィルター</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>「着手前」ステータスのみ表示。出勤したパートが即「今日やれるタスク」を選べる。</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>要対応セクション</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>画面上部に赤枠で固定表示。着手前かつ「期限超過」または「急ぎ」優先度のタスクが自動で最上段に集約。</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>対応中タスクの表示</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>着手者アバターを通常より大きく（22px）青枠＋太字で強調。誰かがやっている作業を一目で判別、重複着手を防止。</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>ステータスKPIカード</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>全タスク／着手前／対応中／完了 の4枚。クリックで該当ステータスにフィルター切替。</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>「自分が着手中」フィルター</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>ボタンで自分が着手or主担当のタスクのみ表示可能。途中で帰った後に再開する用。</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>グループ化</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>デフォルト：フェーズ別。「📋 案件別」ボタンで案件別グループに切替可能。</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>操作ボタン</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>▶ 着手する（緑）／ ✅ 完了にする（青）／ ✅ 完了（バッジ）の3状態のみ。着手中→着手前への戻し機能は提供しない。</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>■ ダッシュボード（経営者・管理者向け）</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>KPIカード（5枚）</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="inlineStr">
+        <is>
+          <t>総案件数 / 対応中タスク / 完了案件 / 検討中案件 / メンバー数。経営者が全体俯瞰するための数値。</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>最近の案件</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>最新5件の案件カード。受注担当者アバター付き。</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>期限が近いタスク</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>期限指定された未完了タスクを期限昇順で最大8件。担当者アバター付き。</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>マイタスク表示</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>提供しない（複数パートが日替わりで動く運用に合わないため削除済み）。現場は /tasks で完結。</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>■ インライン編集（InlineEdit）の見た目</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>見た目</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>通常表示</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>値の下に点線アンダーライン。クリック可能なことを視覚的に示す。</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>ホバー時</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>薄い青背景（hover:bg-blue-50）に変化。tooltip「クリックして入力」を表示。</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>空欄時</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>薄いグレーで「クリックして入力」「クリックして選択」「クリックして日付入力」プレースホルダ。</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>編集中</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>input/select/textarea に切替。Enter or Blur で保存、Escでキャンセル。</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>